--- a/mode_docx_gen/pmi_tokzdzt/tkzdz_modes/ТК ЗДЗ_1.xlsx
+++ b/mode_docx_gen/pmi_tokzdzt/tkzdz_modes/ТК ЗДЗ_1.xlsx
@@ -781,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -813,8 +813,6 @@
     <col width="20" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="20" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -865,7 +863,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NaOtkl_hvptoc1_tovctoc</t>
+          <t>NaOtkl_tovctoc</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -875,100 +873,90 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>NaOtkl_ptoc1_tovctoc</t>
+          <t>OV_ptoc2_tovctoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>OV_ptoc2_tovctoc</t>
+          <t>OV_ptoc1_lvarctoc</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>NaOtkl_ptoc2_tovctoc</t>
+          <t>OV_ptoc1_ltcblktoc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>OV_ptoc1_lvarctoc</t>
+          <t>OV_strpalc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>OV_ptoc1_ltcblktoc</t>
+          <t>OV_hvptoc1_strpalc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>OV_strpalc</t>
+          <t>OV_lvptoc1_strpalc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>OV_hvptoc1_strpalc</t>
+          <t>OV_lvptoc2_strpalc</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>OV_lvptoc1_strpalc</t>
+          <t>OV_tpalc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>OV_lvptoc2_strpalc</t>
+          <t>OV_hvptoc1_tpalc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>OV_tpalc</t>
+          <t>OV_lvptoc1_tpalc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>OV_hvptoc1_tpalc</t>
+          <t>OV_lvptoc2_tpalc</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>OV_lvptoc1_tpalc</t>
+          <t>OV_eqpalc</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>OV_lvptoc2_tpalc</t>
+          <t>NaSign_eqpalc</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>OV_eqpalc</t>
+          <t>otkaz_so</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>NaSign_eqpalc</t>
+          <t>t_masla_zpo</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>otkaz_so</t>
+          <t>OV_tprmofflvlgc</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>t_masla_zpo</t>
+          <t>OV_ptrc1_tprmofflvlgc</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>OV_rbre1_tprmofflvlgc</t>
         </is>
@@ -1060,12 +1048,6 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1246,7 +1228,7 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>srab_tovctocc</t>
+          <t>srab_tovctoc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
